--- a/artfynd/A 18397-2024 artfynd.xlsx
+++ b/artfynd/A 18397-2024 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>117024853</v>
       </c>
       <c r="B14" t="n">
-        <v>57297</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 18397-2024 artfynd.xlsx
+++ b/artfynd/A 18397-2024 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>117024853</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 18397-2024 artfynd.xlsx
+++ b/artfynd/A 18397-2024 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>117024853</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 18397-2024 artfynd.xlsx
+++ b/artfynd/A 18397-2024 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>117024853</v>
       </c>
       <c r="B14" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 18397-2024 artfynd.xlsx
+++ b/artfynd/A 18397-2024 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>117024853</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
